--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-26).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-26).xlsx
@@ -912,69 +912,69 @@
   </si>
   <si>
     <t>214
-167</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 1.700.173,24</t>
-  </si>
-  <si>
-    <t>R$ 9.551,54
-R$ 9.715,49</t>
-  </si>
-  <si>
-    <t>(3.8%)
-(2.8%)</t>
+170</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.737.341,01</t>
+  </si>
+  <si>
+    <t>R$ 9.545,83
+R$ 9.740,67</t>
+  </si>
+  <si>
+    <t>(4.3%)
+(2.9%)</t>
   </si>
   <si>
     <t>98.3</t>
   </si>
   <si>
-    <t>(8.6%)</t>
-  </si>
-  <si>
-    <t>45.3%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
+    <t>(8.9%)</t>
+  </si>
+  <si>
+    <t>45.8%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
   </si>
   <si>
     <t>2.6%</t>
   </si>
   <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>28.7</t>
-  </si>
-  <si>
-    <t>64.8%</t>
-  </si>
-  <si>
-    <t>13.7%</t>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>64.6%</t>
+  </si>
+  <si>
+    <t>14.3%</t>
   </si>
   <si>
     <t>6.7</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>13.3</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>65.9%</t>
-  </si>
-  <si>
-    <t>-R$ 46.263,53</t>
-  </si>
-  <si>
-    <t>2.95</t>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>13.9</t>
+  </si>
+  <si>
+    <t>20.8</t>
+  </si>
+  <si>
+    <t>65.1%</t>
+  </si>
+  <si>
+    <t>-R$ 50.719,26</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -1884,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>4.5</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>11.523903000000001</v>
+      </c>
       <c r="AD4" s="8">
         <v>16.763157894736842</v>
       </c>
@@ -2630,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>1.8843920634920635</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>8.3037030000000005</v>
+      </c>
       <c r="AD10" s="8">
         <v>15.253439682539682</v>
       </c>
@@ -4382,7 +4386,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4418,25 +4422,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>11175.92</v>
+      </c>
+      <c r="P24" s="5">
+        <v>11175.92</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>0.0037884843727264972</v>
+      </c>
+      <c r="R24" s="7">
+        <v>125</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0.0080645161290322509</v>
+      </c>
+      <c r="T24" s="6">
+        <v>-0.00072656210853334663</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.32657177216730254</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.013464126443281627</v>
+      </c>
+      <c r="W24" s="6">
+        <v>-0.0034991302729439726</v>
+      </c>
+      <c r="X24" s="8">
+        <v>34.328471874999998</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>7.7436636363636362</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>10.771701041666667</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>25.497569791666667</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.39583333333333331</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-538.34000000000003</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -4948,7 +4986,9 @@
       <c r="AB28" s="8">
         <v>9.2279999999999998</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="8">
+        <v>11.186332999999999</v>
+      </c>
       <c r="AD28" s="8">
         <v>18.136333999999998</v>
       </c>
@@ -5077,7 +5117,9 @@
       <c r="AB29" s="8">
         <v>12.251551162790697</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>23.962057000000001</v>
+      </c>
       <c r="AD29" s="8">
         <v>31.376136363636363</v>
       </c>
@@ -5202,7 +5244,9 @@
       <c r="AB30" s="8">
         <v>2.5038899999999997</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>5.5999990000000004</v>
+      </c>
       <c r="AD30" s="8">
         <v>12.567223333333335</v>
       </c>
@@ -5593,7 +5637,9 @@
       <c r="AB33" s="8">
         <v>7.3997017857142859</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>9.3735110000000006</v>
+      </c>
       <c r="AD33" s="8">
         <v>16.330058928571429</v>
       </c>
@@ -5696,10 +5742,10 @@
         <v>-0.027472527472527486</v>
       </c>
       <c r="T34" s="6">
-        <v>0.0008885564472617169</v>
+        <v>0.071485535635879421</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.33966026799898485</v>
+        <v>-0.26906328881036712</v>
       </c>
       <c r="V34" s="6">
         <v>0.054479872022296927</v>
@@ -6345,7 +6391,9 @@
       <c r="AB39" s="8">
         <v>6.8946666666666667</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>10.537958</v>
+      </c>
       <c r="AD39" s="8">
         <v>17.718929629629631</v>
       </c>
@@ -6448,10 +6496,10 @@
         <v>0.084415584415584499</v>
       </c>
       <c r="T40" s="6">
-        <v>0.34495409822220346</v>
+        <v>0.33891702208521601</v>
       </c>
       <c r="U40" s="6">
-        <v>0.035164815675013721</v>
+        <v>0.029127739538026269</v>
       </c>
       <c r="V40" s="6">
         <v>0.024559745506242698</v>
@@ -7093,7 +7141,9 @@
       <c r="AB45" s="8">
         <v>4.9459770114942527</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>8.3404209999999992</v>
+      </c>
       <c r="AD45" s="8">
         <v>14.42191011235955</v>
       </c>
@@ -7738,7 +7788,9 @@
       <c r="AB50" s="8">
         <v>10.370164197530864</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>13.968517</v>
+      </c>
       <c r="AD50" s="8">
         <v>21.914814814814815</v>
       </c>
@@ -8091,7 +8143,9 @@
       <c r="AB53" s="8">
         <v>4.6651522727272727</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>8.3893930000000001</v>
+      </c>
       <c r="AD53" s="8">
         <v>15.330302272727273</v>
       </c>
@@ -8220,7 +8274,9 @@
       <c r="AB54" s="8">
         <v>13.025</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>20.247057999999999</v>
+      </c>
       <c r="AD54" s="8">
         <v>27.165195588235296</v>
       </c>
@@ -8349,7 +8405,9 @@
       <c r="AB55" s="8">
         <v>17.132375862068965</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>21.328396999999999</v>
+      </c>
       <c r="AD55" s="8">
         <v>28.218965517241383</v>
       </c>
@@ -9000,7 +9058,9 @@
       <c r="AB60" s="8">
         <v>3.1764948717948718</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>5.8161839999999998</v>
+      </c>
       <c r="AD60" s="8">
         <v>13.310163414634145</v>
       </c>
@@ -9309,7 +9369,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>44</v>
@@ -9345,11 +9405,21 @@
       <c t="s" r="N63" s="4">
         <v>52</v>
       </c>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="6"/>
+      <c r="O63" s="5">
+        <v>0</v>
+      </c>
+      <c r="P63" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R63" s="7">
+        <v>0</v>
+      </c>
+      <c r="S63" s="6">
+        <v>-1</v>
+      </c>
       <c r="T63" s="6"/>
       <c r="U63" s="6"/>
       <c r="V63" s="6"/>
@@ -9363,7 +9433,9 @@
       <c r="AD63" s="8"/>
       <c r="AE63" s="6"/>
       <c r="AF63" s="9"/>
-      <c r="AG63" s="5"/>
+      <c r="AG63" s="5">
+        <v>0</v>
+      </c>
       <c r="AH63" s="10">
         <v>3</v>
       </c>
@@ -10353,7 +10425,9 @@
       <c r="AB71" s="8">
         <v>7.1271106666666677</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>11.477111000000001</v>
+      </c>
       <c r="AD71" s="8">
         <v>19.079653246753246</v>
       </c>
@@ -10831,7 +10905,9 @@
       <c r="AB75" s="8">
         <v>6.3170948717948718</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>12.686752</v>
+      </c>
       <c r="AD75" s="8">
         <v>19.629058974358976</v>
       </c>
@@ -10882,7 +10958,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10916,25 +10992,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>11076.360000000001</v>
+      </c>
+      <c r="P76" s="5">
+        <v>11076.360000000001</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>0.088510864117456345</v>
+      </c>
+      <c r="R76" s="7">
+        <v>123</v>
+      </c>
+      <c r="S76" s="6">
+        <v>0.060344827586206851</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.056000111950135233</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.32406337461043155</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.076334599092120509</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.060579423204012869</v>
+      </c>
+      <c r="X76" s="8">
+        <v>54.98564861111111</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>6.5527559055118116</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>26.282176388888889</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>32.729323999999998</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>41.696065277777777</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.1111111111111111</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>-176.80000000000001</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -12464,7 +12576,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12503,7 +12615,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12537,25 +12649,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>11174.9</v>
+      </c>
+      <c r="P89" s="5">
+        <v>11174.9</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.23603643267181817</v>
+      </c>
+      <c r="R89" s="7">
+        <v>102</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.22727272727272729</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.78436998093942678</v>
+      </c>
+      <c r="U89" s="6">
+        <v>0.45788831219966175</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.023097119437310402</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.010808866298579854</v>
+      </c>
+      <c r="X89" s="8">
+        <v>43.499019607843131</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.56862745098039214</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>13.918300980392157</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>11.387907843137256</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>34.191176470588232</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.078431372549019607</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -12674,7 +12820,9 @@
       <c r="AB90" s="8">
         <v>13.336616666666666</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>46.183802</v>
+      </c>
       <c r="AD90" s="8">
         <v>49.967777333333331</v>
       </c>
@@ -15039,7 +15187,9 @@
       <c r="AB109" s="8">
         <v>15.977631578947367</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>21.759682000000002</v>
+      </c>
       <c r="AD109" s="8">
         <v>29.77061315789474</v>
       </c>
@@ -16481,7 +16631,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17112,7 +17262,9 @@
       <c r="AB126" s="8">
         <v>7.9961099999999998</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>11.980454</v>
+      </c>
       <c r="AD126" s="8">
         <v>18.972223333333332</v>
       </c>
@@ -18428,7 +18580,7 @@
         <v>-556.25</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -19882,10 +20034,10 @@
         <v>-0.25</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
+        <v>1.4307893305266146</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.29218159312826941</v>
+        <v>1.1386077373983452</v>
       </c>
       <c r="V148" s="6">
         <v>0.02409530623588264</v>
@@ -20529,7 +20681,9 @@
       <c r="AB153" s="8">
         <v>8.9364337209302338</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>15.045508</v>
+      </c>
       <c r="AD153" s="8">
         <v>21.982777777777777</v>
       </c>
@@ -20668,7 +20822,7 @@
         <v>388.19999999999999</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -21618,7 +21772,9 @@
       <c r="AB162" s="8">
         <v>4.1686999999999994</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>13.888617</v>
+      </c>
       <c r="AD162" s="8">
         <v>21.824390243902439</v>
       </c>
@@ -22104,7 +22260,9 @@
       <c r="AB166" s="8">
         <v>21.958640740740741</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>26.693698000000001</v>
+      </c>
       <c r="AD166" s="8">
         <v>33.739507407407409</v>
       </c>
@@ -23019,7 +23177,9 @@
       <c r="AB173" s="8">
         <v>11.20673829787234</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>17.945827000000001</v>
+      </c>
       <c r="AD173" s="8">
         <v>23.061727777777779</v>
       </c>
@@ -24321,7 +24481,9 @@
       <c r="AB183" s="8">
         <v>3.7958339285714287</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>8.3749990000000007</v>
+      </c>
       <c r="AD183" s="8">
         <v>15.616666666666667</v>
       </c>
@@ -24805,7 +24967,9 @@
       <c r="AB187" s="8">
         <v>6.2127470588235294</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>13.839214999999999</v>
+      </c>
       <c r="AD187" s="8">
         <v>20.812747058823533</v>
       </c>
@@ -25067,7 +25231,9 @@
       <c r="AB189" s="8">
         <v>12.976271186440679</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>16.813098</v>
+      </c>
       <c r="AD189" s="8">
         <v>23.546111666666665</v>
       </c>
@@ -25196,7 +25362,9 @@
       <c r="AB190" s="8">
         <v>3.9844096774193547</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>8.7505369999999996</v>
+      </c>
       <c r="AD190" s="8">
         <v>15.713441935483869</v>
       </c>
@@ -25976,7 +26144,9 @@
       <c r="AB196" s="8">
         <v>16.039390909090908</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>33.332447999999999</v>
+      </c>
       <c r="AD196" s="8">
         <v>41.2303</v>
       </c>
@@ -26367,7 +26537,9 @@
       <c r="AB199" s="8">
         <v>29.639189189189192</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>72.861118000000005</v>
+      </c>
       <c r="AD199" s="8">
         <v>80.106305405405408</v>
       </c>
@@ -26496,7 +26668,9 @@
       <c r="AB200" s="8">
         <v>3.6297642857142853</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>9.6730940000000007</v>
+      </c>
       <c r="AD200" s="8">
         <v>16.539285714285715</v>
       </c>
@@ -27069,7 +27243,9 @@
       <c r="AB205" s="8">
         <v>2.7760000000000002</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>8.6348880000000001</v>
+      </c>
       <c r="AD205" s="8">
         <v>14.766048148148148</v>
       </c>
@@ -27247,7 +27423,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -27283,25 +27459,57 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>3740.5900000000001</v>
+      </c>
+      <c r="P207" s="5">
+        <v>3740.5900000000001</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>40</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
-      <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="T207" s="6">
+        <v>0.0030259932256676086</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.31803833085155014</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.10249519460833718</v>
+      </c>
+      <c r="W207" s="6">
+        <v>0.062055050139149172</v>
+      </c>
+      <c r="X207" s="8">
+        <v>28.031578947368423</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>7.4258763157894734</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>7.4447368421052627</v>
+      </c>
+      <c r="AC207" s="8">
+        <v>14.357236</v>
+      </c>
+      <c r="AD207" s="8">
+        <v>21.077194736842106</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.78947368421052633</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-3740.5900000000001</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-26).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-26).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.737.341,01</t>
-  </si>
-  <si>
-    <t>R$ 9.545,83
-R$ 9.740,67</t>
-  </si>
-  <si>
-    <t>(4.3%)
-(2.9%)</t>
-  </si>
-  <si>
-    <t>98.3</t>
-  </si>
-  <si>
-    <t>(8.9%)</t>
-  </si>
-  <si>
-    <t>45.8%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
+176</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R$ 1.782.220,44</t>
+  </si>
+  <si>
+    <t>R$ 9.479,90
+R$ 9.663,59</t>
+  </si>
+  <si>
+    <t>(4.6%)
+(3.3%)</t>
+  </si>
+  <si>
+    <t>97.6</t>
+  </si>
+  <si>
+    <t>(9.1%)</t>
+  </si>
+  <si>
+    <t>45.3%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -947,31 +947,31 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>64.6%</t>
-  </si>
-  <si>
-    <t>14.3%</t>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>64.9%</t>
+  </si>
+  <si>
+    <t>14.2%</t>
   </si>
   <si>
     <t>6.7</t>
   </si>
   <si>
-    <t>7.2</t>
+    <t>7.1</t>
   </si>
   <si>
     <t>13.9</t>
   </si>
   <si>
-    <t>20.8</t>
-  </si>
-  <si>
-    <t>65.1%</t>
-  </si>
-  <si>
-    <t>-R$ 50.719,26</t>
+    <t>20.7</t>
+  </si>
+  <si>
+    <t>65.0%</t>
+  </si>
+  <si>
+    <t>-R$ 50.907,86</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>13346</v>
+      </c>
+      <c r="P6" s="5">
+        <v>13346</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.054093160794621564</v>
+      </c>
+      <c r="R6" s="7">
+        <v>127</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.023076923076923106</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.27207639742244871</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.024735381387681703</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.023684130076427393</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-8.0293720965083178E-05</v>
+      </c>
+      <c r="X6" s="8">
+        <v>21.231754736842102</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.97894736842105268</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.5958992063492063</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.083864893617021</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>7.939254</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>14.835263157894737</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.96842105263157896</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -3025,7 +3061,9 @@
       <c r="AB13" s="8">
         <v>10.398863636363636</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>19.183693999999999</v>
+      </c>
       <c r="AD13" s="8">
         <v>25.997565168539328</v>
       </c>
@@ -5956,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5992,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>6984.4200000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6984.4200000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.1082907124308341</v>
+      </c>
+      <c r="R36" s="7">
+        <v>69</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.10389610389610393</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.32955071430412264</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.040284032174468312</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.078485686714143771</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.044258077263394813</v>
+      </c>
+      <c r="X36" s="8">
+        <v>28.0639875</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.035714285714285712</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.7862749999999998</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.1720232142857148</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>12.122915000000001</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>19.074405357142858</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.6785714285714286</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6706,7 +6780,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6742,25 +6816,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>8615.9500000000007</v>
+      </c>
+      <c r="P42" s="5">
+        <v>8615.9500000000007</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-0.26342340832791189</v>
+      </c>
+      <c r="R42" s="7">
+        <v>89</v>
+      </c>
+      <c r="S42" s="6">
+        <v>-0.19090909090909092</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.3544654042792727</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.039692221983646608</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.043557413866143604</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.016126892565532527</v>
+      </c>
+      <c r="X42" s="8">
+        <v>26.924528301886792</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.037735849056603772</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.5558939024390241</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>7.325961538461538</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>13.372501</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>20.147484905660377</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.64150943396226412</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>-125.8</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7841,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7877,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1098.1500000000001</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1098.1500000000001</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.48744457409568254</v>
+      </c>
+      <c r="R51" s="7">
+        <v>11</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.42105263157894735</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.32035696398488367</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.035441879524655093</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.093101579929882078</v>
+      </c>
+      <c r="X51" s="8">
+        <v>12.220825</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.8287909090909094</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>0.55835000000000001</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>6.1041660000000002</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>11.279175</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>1</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -14270,7 +14416,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14306,25 +14452,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>7308.1899999999996</v>
+      </c>
+      <c r="P102" s="5">
+        <v>7308.1899999999996</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.26995047220229884</v>
+      </c>
+      <c r="R102" s="7">
+        <v>81</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.21359223300970875</v>
+      </c>
+      <c r="T102" s="6">
+        <v>-0.00094277789712637471</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.33010362346901218</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.025094585663481654</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.009707738851890824</v>
+      </c>
+      <c r="X102" s="8">
+        <v>37.234905660377358</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.13207547169811321</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.39622641509433965</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>11.627642682926828</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>6.859524489795918</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>18.195886000000002</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>24.5261</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.30188679245283018</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -21216,7 +21398,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21252,25 +21434,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>7526.7200000000003</v>
+      </c>
+      <c r="P158" s="5">
+        <v>7526.7200000000003</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.12283862637036069</v>
+      </c>
+      <c r="R158" s="7">
+        <v>74</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.1685393258426966</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.34834040591386423</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.026275814697504358</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.04403916978444794</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.01366471716763743</v>
+      </c>
+      <c r="X158" s="8">
+        <v>31.17450980392157</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.72549019607843135</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.6539999999999999</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>5.1411764705882348</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>11.634765</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>18.620260784313725</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.35294117647058826</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>-62.799999999999997</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -26015,7 +26233,9 @@
       <c r="AB195" s="8">
         <v>7.2145828124999998</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>13.804264999999999</v>
+      </c>
       <c r="AD195" s="8">
         <v>20.621354687499998</v>
       </c>
